--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VFPractitionerCountry</t>
+    <t>http://va.gov/fhir/ConceptMap/CMVFPractitionerCountry</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFPractitionerCountry</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry</t>
   </si>
   <si>
     <t>Display</t>
@@ -105,10 +105,13 @@
     <t>Target</t>
   </si>
   <si>
+    <t>http://va.gov/terminology/vistaDefinedElements/200-.1215</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>undefined</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>ALABAMA</t>
@@ -712,7 +715,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -720,16 +723,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>20</v>
@@ -737,16 +740,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>20</v>
@@ -754,50 +757,50 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>20</v>
@@ -805,16 +808,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>20</v>
@@ -822,16 +825,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>20</v>
@@ -839,16 +842,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>20</v>
@@ -856,16 +859,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>20</v>
@@ -873,33 +876,33 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s" s="2">
         <v>20</v>
@@ -907,33 +910,33 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s" s="2">
         <v>20</v>
@@ -941,16 +944,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s" s="2">
         <v>20</v>
@@ -958,16 +961,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s" s="2">
         <v>20</v>
@@ -975,16 +978,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s" s="2">
         <v>20</v>
@@ -992,33 +995,33 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s" s="2">
         <v>20</v>
@@ -1026,16 +1029,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s" s="2">
         <v>20</v>
@@ -1043,33 +1046,33 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s" s="2">
         <v>20</v>
@@ -1077,16 +1080,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s" s="2">
         <v>20</v>
@@ -1094,16 +1097,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" t="s" s="2">
         <v>20</v>
@@ -1111,16 +1114,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" t="s" s="2">
         <v>20</v>
@@ -1128,16 +1131,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>20</v>
@@ -1145,16 +1148,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s" s="2">
         <v>20</v>
@@ -1162,16 +1165,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s" s="2">
         <v>20</v>
@@ -1179,16 +1182,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s" s="2">
         <v>20</v>
@@ -1196,16 +1199,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s" s="2">
         <v>20</v>
@@ -1213,50 +1216,50 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s" s="2">
         <v>20</v>
@@ -1264,16 +1267,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s" s="2">
         <v>20</v>
@@ -1281,16 +1284,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s" s="2">
         <v>20</v>
@@ -1298,16 +1301,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s" s="2">
         <v>20</v>
@@ -1315,16 +1318,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s" s="2">
         <v>20</v>
@@ -1332,16 +1335,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s" s="2">
         <v>20</v>
@@ -1349,16 +1352,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s" s="2">
         <v>20</v>
@@ -1366,16 +1369,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E41" t="s" s="2">
         <v>20</v>
@@ -1383,16 +1386,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E42" t="s" s="2">
         <v>20</v>
@@ -1400,16 +1403,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s" s="2">
         <v>20</v>
@@ -1417,33 +1420,33 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s" s="2">
         <v>20</v>
@@ -1451,16 +1454,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s" s="2">
         <v>20</v>
@@ -1468,16 +1471,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s" s="2">
         <v>20</v>
@@ -1485,16 +1488,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s" s="2">
         <v>20</v>
@@ -1502,33 +1505,33 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E50" t="s" s="2">
         <v>20</v>
@@ -1536,16 +1539,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51" t="s" s="2">
         <v>20</v>
@@ -1553,84 +1556,84 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E56" t="s" s="2">
         <v>20</v>
@@ -1638,16 +1641,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>20</v>
@@ -1655,33 +1658,33 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E59" t="s" s="2">
         <v>20</v>
@@ -1689,33 +1692,33 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E61" t="s" s="2">
         <v>20</v>
@@ -1723,84 +1726,84 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>20</v>
@@ -1808,33 +1811,33 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E68" t="s" s="2">
         <v>20</v>
@@ -1842,16 +1845,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E69" t="s" s="2">
         <v>20</v>
@@ -1859,16 +1862,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E70" t="s" s="2">
         <v>20</v>
@@ -1876,16 +1879,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E71" t="s" s="2">
         <v>20</v>
@@ -1893,33 +1896,33 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E73" t="s" s="2">
         <v>20</v>
@@ -1927,16 +1930,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E74" t="s" s="2">
         <v>20</v>
@@ -1944,33 +1947,33 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s" s="2">
         <v>20</v>
@@ -1978,16 +1981,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E77" t="s" s="2">
         <v>20</v>
@@ -1995,16 +1998,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s" s="2">
         <v>20</v>
@@ -2012,16 +2015,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s" s="2">
         <v>20</v>
@@ -2029,16 +2032,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E80" t="s" s="2">
         <v>20</v>
@@ -2046,19 +2049,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t/>
   </si>
   <si>
-    <t>undefined</t>
+    <t>null</t>
   </si>
   <si>
     <t>ALABAMA</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="164">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,6 +135,9 @@
     <t>Canada</t>
   </si>
   <si>
+    <t>AMERICAN_SAMOA</t>
+  </si>
+  <si>
     <t>AMERICAN SAMOA</t>
   </si>
   <si>
@@ -150,15 +153,27 @@
     <t>ARKANSAS</t>
   </si>
   <si>
+    <t>ARMED_FORCES_AF,EU,ME,CA</t>
+  </si>
+  <si>
     <t>ARMED FORCES AF,EU,ME,CA</t>
   </si>
   <si>
+    <t>ARMED_FORCES_AMER_(EXC_CANADA)</t>
+  </si>
+  <si>
     <t>ARMED FORCES AMER (EXC CANADA)</t>
   </si>
   <si>
+    <t>ARMED_FORCES_PACIFIC</t>
+  </si>
+  <si>
     <t>ARMED FORCES PACIFIC</t>
   </si>
   <si>
+    <t>BRITISH_COLUMBIA</t>
+  </si>
+  <si>
     <t>BRITISH COLUMBIA</t>
   </si>
   <si>
@@ -177,9 +192,15 @@
     <t>DELAWARE</t>
   </si>
   <si>
+    <t>DISTRICT_OF_COLUMBIA</t>
+  </si>
+  <si>
     <t>DISTRICT OF COLUMBIA</t>
   </si>
   <si>
+    <t>FEDERATED_STATES_OF_MICRONESIA</t>
+  </si>
+  <si>
     <t>FEDERATED STATES OF MICRONESIA</t>
   </si>
   <si>
@@ -234,6 +255,9 @@
     <t>MANITOBA</t>
   </si>
   <si>
+    <t>MARSHALL_ISLANDS</t>
+  </si>
+  <si>
     <t>MARSHALL ISLANDS</t>
   </si>
   <si>
@@ -273,30 +297,54 @@
     <t>NEVADA</t>
   </si>
   <si>
+    <t>NEW_BRUNSWICK</t>
+  </si>
+  <si>
     <t>NEW BRUNSWICK</t>
   </si>
   <si>
+    <t>NEW_HAMPSHIRE</t>
+  </si>
+  <si>
     <t>NEW HAMPSHIRE</t>
   </si>
   <si>
+    <t>NEW_JERSEY</t>
+  </si>
+  <si>
     <t>NEW JERSEY</t>
   </si>
   <si>
+    <t>NEW_MEXICO</t>
+  </si>
+  <si>
     <t>NEW MEXICO</t>
   </si>
   <si>
+    <t>NEW_YORK</t>
+  </si>
+  <si>
     <t>NEW YORK</t>
   </si>
   <si>
     <t>NEWFOUNDLAND</t>
   </si>
   <si>
+    <t>NORTH_CAROLINA</t>
+  </si>
+  <si>
     <t>NORTH CAROLINA</t>
   </si>
   <si>
+    <t>NORTH_DAKOTA</t>
+  </si>
+  <si>
     <t>NORTH DAKOTA</t>
   </si>
   <si>
+    <t>NORTHERN_MARIANA_ISLANDS</t>
+  </si>
+  <si>
     <t>NORTHERN MARIANA ISLANDS</t>
   </si>
   <si>
@@ -306,12 +354,21 @@
     <t>Northern Mariana Islands</t>
   </si>
   <si>
+    <t>NORTHWEST_TERRITORIES</t>
+  </si>
+  <si>
     <t>NORTHWEST TERRITORIES</t>
   </si>
   <si>
+    <t>NOVA_SCOTIA</t>
+  </si>
+  <si>
     <t>NOVA SCOTIA</t>
   </si>
   <si>
+    <t>NUNAVUT_PROVINCE</t>
+  </si>
+  <si>
     <t>NUNAVUT PROVINCE</t>
   </si>
   <si>
@@ -348,9 +405,15 @@
     <t>Phillipines</t>
   </si>
   <si>
+    <t>PRINCE_EDWARD_ISLAND</t>
+  </si>
+  <si>
     <t>PRINCE EDWARD ISLAND</t>
   </si>
   <si>
+    <t>PUERTO_RICO</t>
+  </si>
+  <si>
     <t>PUERTO RICO</t>
   </si>
   <si>
@@ -363,15 +426,24 @@
     <t>QUEBEC</t>
   </si>
   <si>
+    <t>RHODE_ISLAND</t>
+  </si>
+  <si>
     <t>RHODE ISLAND</t>
   </si>
   <si>
     <t>SASKATCHEWAN</t>
   </si>
   <si>
+    <t>SOUTH_CAROLINA</t>
+  </si>
+  <si>
     <t>SOUTH CAROLINA</t>
   </si>
   <si>
+    <t>SOUTH_DAKOTA</t>
+  </si>
+  <si>
     <t>SOUTH DAKOTA</t>
   </si>
   <si>
@@ -381,6 +453,9 @@
     <t>TEXAS</t>
   </si>
   <si>
+    <t>U.S._MINOR_OUTLYING_ISLANDS</t>
+  </si>
+  <si>
     <t>U.S. MINOR OUTLYING ISLANDS</t>
   </si>
   <si>
@@ -396,6 +471,9 @@
     <t>VERMONT</t>
   </si>
   <si>
+    <t>VIRGIN_ISLANDS</t>
+  </si>
+  <si>
     <t>VIRGIN ISLANDS</t>
   </si>
   <si>
@@ -411,6 +489,9 @@
     <t>WASHINGTON</t>
   </si>
   <si>
+    <t>WEST_VIRGINIA</t>
+  </si>
+  <si>
     <t>WEST VIRGINIA</t>
   </si>
   <si>
@@ -418,6 +499,9 @@
   </si>
   <si>
     <t>WYOMING</t>
+  </si>
+  <si>
+    <t>YUKON_TERRITORY</t>
   </si>
   <si>
     <t>YUKON TERRITORY</t>
@@ -777,24 +861,24 @@
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>34</v>
@@ -808,10 +892,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>34</v>
@@ -825,10 +909,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>34</v>
@@ -842,10 +926,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>34</v>
@@ -859,10 +943,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>34</v>
@@ -876,10 +960,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>34</v>
@@ -893,10 +977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>34</v>
@@ -910,10 +994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>34</v>
@@ -927,10 +1011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>34</v>
@@ -944,10 +1028,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>34</v>
@@ -961,10 +1045,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>34</v>
@@ -978,10 +1062,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>34</v>
@@ -995,27 +1079,27 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>34</v>
@@ -1029,10 +1113,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>34</v>
@@ -1046,27 +1130,27 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>34</v>
@@ -1080,10 +1164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>34</v>
@@ -1097,10 +1181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>34</v>
@@ -1114,10 +1198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>34</v>
@@ -1131,10 +1215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>34</v>
@@ -1148,10 +1232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>34</v>
@@ -1165,10 +1249,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>34</v>
@@ -1182,10 +1266,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>34</v>
@@ -1199,10 +1283,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>34</v>
@@ -1216,10 +1300,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>34</v>
@@ -1233,27 +1317,27 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>34</v>
@@ -1267,10 +1351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>34</v>
@@ -1284,10 +1368,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>34</v>
@@ -1301,10 +1385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>34</v>
@@ -1318,10 +1402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>34</v>
@@ -1335,10 +1419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>34</v>
@@ -1352,10 +1436,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>34</v>
@@ -1369,10 +1453,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>34</v>
@@ -1386,10 +1470,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>34</v>
@@ -1403,10 +1487,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>34</v>
@@ -1420,10 +1504,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>34</v>
@@ -1437,10 +1521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>34</v>
@@ -1454,10 +1538,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>34</v>
@@ -1471,10 +1555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>34</v>
@@ -1488,10 +1572,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>34</v>
@@ -1505,10 +1589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>34</v>
@@ -1522,10 +1606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>34</v>
@@ -1539,10 +1623,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>34</v>
@@ -1556,27 +1640,27 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>34</v>
@@ -1590,10 +1674,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>34</v>
@@ -1607,10 +1691,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>34</v>
@@ -1624,10 +1708,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>34</v>
@@ -1641,10 +1725,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>34</v>
@@ -1658,10 +1742,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>34</v>
@@ -1675,10 +1759,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>34</v>
@@ -1692,27 +1776,27 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>34</v>
@@ -1726,27 +1810,27 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>34</v>
@@ -1760,27 +1844,27 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>34</v>
@@ -1794,10 +1878,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>34</v>
@@ -1811,10 +1895,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>34</v>
@@ -1828,10 +1912,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>34</v>
@@ -1845,10 +1929,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>34</v>
@@ -1862,10 +1946,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>34</v>
@@ -1879,10 +1963,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>34</v>
@@ -1896,27 +1980,27 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>124</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>34</v>
@@ -1930,10 +2014,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>34</v>
@@ -1947,27 +2031,27 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>129</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>34</v>
@@ -1981,10 +2065,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>34</v>
@@ -1998,10 +2082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>34</v>
@@ -2015,10 +2099,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>34</v>
@@ -2032,10 +2116,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>34</v>
@@ -2049,10 +2133,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>34</v>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="163">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>null</t>
   </si>
   <si>
     <t>ALABAMA</t>
@@ -798,25 +795,23 @@
       <c r="C2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
         <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>20</v>
@@ -824,16 +819,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>20</v>
@@ -841,50 +836,50 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s" s="2">
+      <c r="E5" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
+      <c r="E6" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>20</v>
@@ -892,16 +887,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>20</v>
@@ -909,16 +904,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>47</v>
-      </c>
       <c r="C9" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>20</v>
@@ -926,16 +921,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>49</v>
-      </c>
       <c r="C10" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>20</v>
@@ -943,16 +938,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>51</v>
-      </c>
       <c r="C11" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>20</v>
@@ -960,33 +955,33 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>53</v>
-      </c>
       <c r="C12" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s" s="2">
         <v>20</v>
@@ -994,33 +989,33 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s" s="2">
         <v>20</v>
@@ -1028,16 +1023,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s" s="2">
         <v>20</v>
@@ -1045,16 +1040,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s" s="2">
         <v>20</v>
@@ -1062,16 +1057,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>60</v>
-      </c>
       <c r="C18" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s" s="2">
         <v>20</v>
@@ -1079,33 +1074,33 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="C19" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="C19" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s" s="2">
+      <c r="E19" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s" s="2">
         <v>20</v>
@@ -1113,16 +1108,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s" s="2">
         <v>20</v>
@@ -1130,33 +1125,33 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D22" t="s" s="2">
+      <c r="E22" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s" s="2">
         <v>20</v>
@@ -1164,16 +1159,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s" s="2">
         <v>20</v>
@@ -1181,16 +1176,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s" s="2">
         <v>20</v>
@@ -1198,16 +1193,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s" s="2">
         <v>20</v>
@@ -1215,16 +1210,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>20</v>
@@ -1232,16 +1227,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s" s="2">
         <v>20</v>
@@ -1249,16 +1244,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s" s="2">
         <v>20</v>
@@ -1266,16 +1261,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s" s="2">
         <v>20</v>
@@ -1283,16 +1278,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s" s="2">
         <v>20</v>
@@ -1300,50 +1295,50 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E32" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="B33" t="s" s="2">
+      <c r="C33" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D33" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="C33" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D33" t="s" s="2">
+      <c r="E33" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s" s="2">
         <v>20</v>
@@ -1351,16 +1346,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E35" t="s" s="2">
         <v>20</v>
@@ -1368,16 +1363,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s" s="2">
         <v>20</v>
@@ -1385,16 +1380,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s" s="2">
         <v>20</v>
@@ -1402,16 +1397,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s" s="2">
         <v>20</v>
@@ -1419,16 +1414,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s" s="2">
         <v>20</v>
@@ -1436,16 +1431,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s" s="2">
         <v>20</v>
@@ -1453,16 +1448,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s" s="2">
         <v>20</v>
@@ -1470,16 +1465,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s" s="2">
         <v>20</v>
@@ -1487,16 +1482,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E43" t="s" s="2">
         <v>20</v>
@@ -1504,33 +1499,33 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="B44" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="C44" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="B45" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="C45" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E45" t="s" s="2">
         <v>20</v>
@@ -1538,16 +1533,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="B46" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="C46" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E46" t="s" s="2">
         <v>20</v>
@@ -1555,16 +1550,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="B47" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="C47" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" t="s" s="2">
         <v>20</v>
@@ -1572,16 +1567,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="B48" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="C48" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E48" t="s" s="2">
         <v>20</v>
@@ -1589,33 +1584,33 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="B50" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="C50" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s" s="2">
         <v>20</v>
@@ -1623,16 +1618,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="B51" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="C51" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51" t="s" s="2">
         <v>20</v>
@@ -1640,84 +1635,84 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="B52" t="s" s="2">
+      <c r="C52" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D52" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="C52" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D52" t="s" s="2">
+      <c r="E52" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="B53" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="C53" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E53" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="B54" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="C54" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E54" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="B55" t="s" s="2">
-        <v>118</v>
-      </c>
       <c r="C55" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E56" t="s" s="2">
         <v>20</v>
@@ -1725,16 +1720,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>20</v>
@@ -1742,33 +1737,33 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D58" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E58" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E59" t="s" s="2">
         <v>20</v>
@@ -1776,33 +1771,33 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D60" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="B60" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D60" t="s" s="2">
+      <c r="E60" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E61" t="s" s="2">
         <v>20</v>
@@ -1810,84 +1805,84 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D62" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="B62" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D62" t="s" s="2">
+      <c r="E62" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="B63" t="s" s="2">
-        <v>131</v>
-      </c>
       <c r="C63" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="B64" t="s" s="2">
+      <c r="C64" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D64" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="C64" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D64" t="s" s="2">
+      <c r="E64" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="E64" t="s" s="2">
-        <v>135</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E65" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E65" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="B66" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="C66" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>20</v>
@@ -1895,33 +1890,33 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E67" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E67" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="B68" t="s" s="2">
-        <v>141</v>
-      </c>
       <c r="C68" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E68" t="s" s="2">
         <v>20</v>
@@ -1929,16 +1924,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>143</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E69" t="s" s="2">
         <v>20</v>
@@ -1946,16 +1941,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E70" t="s" s="2">
         <v>20</v>
@@ -1963,16 +1958,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E71" t="s" s="2">
         <v>20</v>
@@ -1980,33 +1975,33 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="B72" t="s" s="2">
+      <c r="C72" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D72" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="C72" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D72" t="s" s="2">
+      <c r="E72" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="E72" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E73" t="s" s="2">
         <v>20</v>
@@ -2014,16 +2009,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E74" t="s" s="2">
         <v>20</v>
@@ -2031,33 +2026,33 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="B75" t="s" s="2">
+      <c r="C75" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D75" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="C75" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D75" t="s" s="2">
+      <c r="E75" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="E75" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" t="s" s="2">
         <v>20</v>
@@ -2065,16 +2060,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E77" t="s" s="2">
         <v>20</v>
@@ -2082,16 +2077,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="B78" t="s" s="2">
-        <v>159</v>
-      </c>
       <c r="C78" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E78" t="s" s="2">
         <v>20</v>
@@ -2099,16 +2094,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E79" t="s" s="2">
         <v>20</v>
@@ -2116,16 +2111,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E80" t="s" s="2">
         <v>20</v>
@@ -2133,19 +2128,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="B81" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="C81" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D81" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/vistaDefinedElements/200-.1215</t>
+    <t>http://va.gov/terminology/vistaDefinedTerms/200-.1215</t>
   </si>
   <si>
     <t/>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="164">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,13 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,6 +93,12 @@
     <t>Source</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry-vista</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry</t>
   </si>
   <si>
@@ -100,9 +106,6 @@
   </si>
   <si>
     <t>Relationship</t>
-  </si>
-  <si>
-    <t>Target</t>
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedTerms/200-.1215</t>
@@ -635,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -756,6 +759,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -773,45 +784,45 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>29</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>20</v>
@@ -819,16 +830,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>20</v>
@@ -836,50 +847,50 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>20</v>
@@ -887,16 +898,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>20</v>
@@ -904,16 +915,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>20</v>
@@ -921,16 +932,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>20</v>
@@ -938,16 +949,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>20</v>
@@ -955,33 +966,33 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s" s="2">
         <v>20</v>
@@ -989,33 +1000,33 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s" s="2">
         <v>20</v>
@@ -1023,16 +1034,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s" s="2">
         <v>20</v>
@@ -1040,16 +1051,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s" s="2">
         <v>20</v>
@@ -1057,16 +1068,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s" s="2">
         <v>20</v>
@@ -1074,33 +1085,33 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s" s="2">
         <v>20</v>
@@ -1108,16 +1119,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s" s="2">
         <v>20</v>
@@ -1125,33 +1136,33 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s" s="2">
         <v>20</v>
@@ -1159,16 +1170,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s" s="2">
         <v>20</v>
@@ -1176,16 +1187,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" t="s" s="2">
         <v>20</v>
@@ -1193,16 +1204,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" t="s" s="2">
         <v>20</v>
@@ -1210,16 +1221,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>20</v>
@@ -1227,16 +1238,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s" s="2">
         <v>20</v>
@@ -1244,16 +1255,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s" s="2">
         <v>20</v>
@@ -1261,16 +1272,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s" s="2">
         <v>20</v>
@@ -1278,16 +1289,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s" s="2">
         <v>20</v>
@@ -1295,50 +1306,50 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s" s="2">
         <v>20</v>
@@ -1346,16 +1357,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s" s="2">
         <v>20</v>
@@ -1363,16 +1374,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s" s="2">
         <v>20</v>
@@ -1380,16 +1391,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s" s="2">
         <v>20</v>
@@ -1397,16 +1408,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s" s="2">
         <v>20</v>
@@ -1414,16 +1425,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s" s="2">
         <v>20</v>
@@ -1431,16 +1442,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s" s="2">
         <v>20</v>
@@ -1448,16 +1459,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E41" t="s" s="2">
         <v>20</v>
@@ -1465,16 +1476,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E42" t="s" s="2">
         <v>20</v>
@@ -1482,16 +1493,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s" s="2">
         <v>20</v>
@@ -1499,33 +1510,33 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s" s="2">
         <v>20</v>
@@ -1533,16 +1544,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s" s="2">
         <v>20</v>
@@ -1550,16 +1561,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s" s="2">
         <v>20</v>
@@ -1567,16 +1578,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s" s="2">
         <v>20</v>
@@ -1584,33 +1595,33 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E50" t="s" s="2">
         <v>20</v>
@@ -1618,16 +1629,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51" t="s" s="2">
         <v>20</v>
@@ -1635,84 +1646,84 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E56" t="s" s="2">
         <v>20</v>
@@ -1720,16 +1731,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>20</v>
@@ -1737,33 +1748,33 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E59" t="s" s="2">
         <v>20</v>
@@ -1771,33 +1782,33 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E61" t="s" s="2">
         <v>20</v>
@@ -1805,84 +1816,84 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>20</v>
@@ -1890,33 +1901,33 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E68" t="s" s="2">
         <v>20</v>
@@ -1924,16 +1935,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E69" t="s" s="2">
         <v>20</v>
@@ -1941,16 +1952,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E70" t="s" s="2">
         <v>20</v>
@@ -1958,16 +1969,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E71" t="s" s="2">
         <v>20</v>
@@ -1975,33 +1986,33 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E73" t="s" s="2">
         <v>20</v>
@@ -2009,16 +2020,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E74" t="s" s="2">
         <v>20</v>
@@ -2026,33 +2037,33 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s" s="2">
         <v>20</v>
@@ -2060,16 +2071,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E77" t="s" s="2">
         <v>20</v>
@@ -2077,16 +2088,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s" s="2">
         <v>20</v>
@@ -2094,16 +2105,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s" s="2">
         <v>20</v>
@@ -2111,16 +2122,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E80" t="s" s="2">
         <v>20</v>
@@ -2128,19 +2139,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/string</t>
   </si>
   <si>
     <t>ALABAMA</t>
@@ -806,23 +809,25 @@
       <c r="C2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>33</v>
+      </c>
       <c r="E2" t="s" s="2">
         <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>20</v>
@@ -830,16 +835,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>20</v>
@@ -847,50 +852,50 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>20</v>
@@ -898,16 +903,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>20</v>
@@ -915,16 +920,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>20</v>
@@ -932,16 +937,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>20</v>
@@ -949,16 +954,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>20</v>
@@ -966,33 +971,33 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s" s="2">
         <v>20</v>
@@ -1000,33 +1005,33 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s" s="2">
         <v>20</v>
@@ -1034,16 +1039,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s" s="2">
         <v>20</v>
@@ -1051,16 +1056,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s" s="2">
         <v>20</v>
@@ -1068,16 +1073,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s" s="2">
         <v>20</v>
@@ -1085,33 +1090,33 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s" s="2">
         <v>20</v>
@@ -1119,16 +1124,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s" s="2">
         <v>20</v>
@@ -1136,33 +1141,33 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s" s="2">
         <v>20</v>
@@ -1170,16 +1175,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s" s="2">
         <v>20</v>
@@ -1187,16 +1192,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s" s="2">
         <v>20</v>
@@ -1204,16 +1209,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26" t="s" s="2">
         <v>20</v>
@@ -1221,16 +1226,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>20</v>
@@ -1238,16 +1243,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s" s="2">
         <v>20</v>
@@ -1255,16 +1260,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E29" t="s" s="2">
         <v>20</v>
@@ -1272,16 +1277,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" t="s" s="2">
         <v>20</v>
@@ -1289,16 +1294,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E31" t="s" s="2">
         <v>20</v>
@@ -1306,50 +1311,50 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E34" t="s" s="2">
         <v>20</v>
@@ -1357,16 +1362,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s" s="2">
         <v>20</v>
@@ -1374,16 +1379,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36" t="s" s="2">
         <v>20</v>
@@ -1391,16 +1396,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s" s="2">
         <v>20</v>
@@ -1408,16 +1413,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38" t="s" s="2">
         <v>20</v>
@@ -1425,16 +1430,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E39" t="s" s="2">
         <v>20</v>
@@ -1442,16 +1447,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s" s="2">
         <v>20</v>
@@ -1459,16 +1464,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E41" t="s" s="2">
         <v>20</v>
@@ -1476,16 +1481,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s" s="2">
         <v>20</v>
@@ -1493,16 +1498,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s" s="2">
         <v>20</v>
@@ -1510,33 +1515,33 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E45" t="s" s="2">
         <v>20</v>
@@ -1544,16 +1549,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s" s="2">
         <v>20</v>
@@ -1561,16 +1566,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E47" t="s" s="2">
         <v>20</v>
@@ -1578,16 +1583,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E48" t="s" s="2">
         <v>20</v>
@@ -1595,33 +1600,33 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E50" t="s" s="2">
         <v>20</v>
@@ -1629,16 +1634,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E51" t="s" s="2">
         <v>20</v>
@@ -1646,84 +1651,84 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E56" t="s" s="2">
         <v>20</v>
@@ -1731,16 +1736,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>20</v>
@@ -1748,33 +1753,33 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E59" t="s" s="2">
         <v>20</v>
@@ -1782,33 +1787,33 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E61" t="s" s="2">
         <v>20</v>
@@ -1816,84 +1821,84 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>20</v>
@@ -1901,33 +1906,33 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E68" t="s" s="2">
         <v>20</v>
@@ -1935,16 +1940,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E69" t="s" s="2">
         <v>20</v>
@@ -1952,16 +1957,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E70" t="s" s="2">
         <v>20</v>
@@ -1969,16 +1974,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E71" t="s" s="2">
         <v>20</v>
@@ -1986,33 +1991,33 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E73" t="s" s="2">
         <v>20</v>
@@ -2020,16 +2025,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E74" t="s" s="2">
         <v>20</v>
@@ -2037,33 +2042,33 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s" s="2">
         <v>20</v>
@@ -2071,16 +2076,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E77" t="s" s="2">
         <v>20</v>
@@ -2088,16 +2093,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E78" t="s" s="2">
         <v>20</v>
@@ -2105,16 +2110,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E79" t="s" s="2">
         <v>20</v>
@@ -2122,16 +2127,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E80" t="s" s="2">
         <v>20</v>
@@ -2139,19 +2144,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>INDIANA</t>
+  </si>
+  <si>
+    <t>source-is-narrower-than-target</t>
   </si>
   <si>
     <t>IOWA</t>
@@ -1215,7 +1218,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>36</v>
@@ -1226,10 +1229,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>35</v>
@@ -1243,10 +1246,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>35</v>
@@ -1260,10 +1263,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>35</v>
@@ -1277,10 +1280,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>35</v>
@@ -1294,10 +1297,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>35</v>
@@ -1311,10 +1314,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>35</v>
@@ -1328,27 +1331,27 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>35</v>
@@ -1362,10 +1365,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>35</v>
@@ -1379,10 +1382,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>35</v>
@@ -1396,10 +1399,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>35</v>
@@ -1413,10 +1416,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>35</v>
@@ -1430,10 +1433,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>35</v>
@@ -1447,10 +1450,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>35</v>
@@ -1464,10 +1467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>35</v>
@@ -1481,10 +1484,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>35</v>
@@ -1498,10 +1501,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>35</v>
@@ -1515,10 +1518,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>35</v>
@@ -1532,10 +1535,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>35</v>
@@ -1549,10 +1552,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>35</v>
@@ -1566,10 +1569,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>35</v>
@@ -1583,10 +1586,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>35</v>
@@ -1600,10 +1603,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>35</v>
@@ -1617,10 +1620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>35</v>
@@ -1634,10 +1637,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>35</v>
@@ -1651,27 +1654,27 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>35</v>
@@ -1685,10 +1688,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>35</v>
@@ -1702,10 +1705,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>35</v>
@@ -1719,10 +1722,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>35</v>
@@ -1736,10 +1739,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>35</v>
@@ -1753,10 +1756,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>35</v>
@@ -1770,10 +1773,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>35</v>
@@ -1787,27 +1790,27 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>35</v>
@@ -1821,27 +1824,27 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>35</v>
@@ -1855,27 +1858,27 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>35</v>
@@ -1889,10 +1892,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>35</v>
@@ -1906,10 +1909,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>35</v>
@@ -1923,10 +1926,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>35</v>
@@ -1940,10 +1943,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>35</v>
@@ -1957,10 +1960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>35</v>
@@ -1974,10 +1977,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>35</v>
@@ -1991,27 +1994,27 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>35</v>
@@ -2025,10 +2028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>35</v>
@@ -2042,27 +2045,27 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>35</v>
@@ -2076,10 +2079,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>35</v>
@@ -2093,10 +2096,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>35</v>
@@ -2110,10 +2113,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>35</v>
@@ -2127,10 +2130,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>35</v>
@@ -2144,10 +2147,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>35</v>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFPractitionerCountry.xlsx
+++ b/docs/CMVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
